--- a/Action-敵追加中-/Data/CSV/Platform/PlatformId.xlsx
+++ b/Action-敵追加中-/Data/CSV/Platform/PlatformId.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8144354F-2B59-45C8-9473-E23C6A59DE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA57F04B-1713-4A3A-BD0B-A794FF44D30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Platform" sheetId="1" r:id="rId1"/>
+    <sheet name="PlatformId" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -600,132 +600,132 @@
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A54">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
